--- a/outputs/tables/top_comments_by_category.xlsx
+++ b/outputs/tables/top_comments_by_category.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="103">
   <si>
     <t>Tag</t>
   </si>
@@ -31,277 +31,283 @@
     <t>ADVANCED LCA: I am interested to learn more about advanced LCA methods</t>
   </si>
   <si>
+    <t>ADVANCED LCA: Whether I use advanced LCA methods depends on (how difficult it is)</t>
+  </si>
+  <si>
     <t>ADVANCED LCA: A barrier to adopting advanced LCA methods may be (learning curve)</t>
   </si>
   <si>
-    <t>ADVANCED LCA: Whether I use advanced LCA methods depends on (how difficult it is)</t>
-  </si>
-  <si>
     <t>APPLICATION</t>
   </si>
   <si>
+    <t>APPLICATION: LCA results are used to inform EC reduction</t>
+  </si>
+  <si>
     <t>APPLICATION: We aspire to (do more LCAs)</t>
   </si>
   <si>
+    <t>APPLICATION: We have worked with a sustainability consultant on the LCA</t>
+  </si>
+  <si>
+    <t>BIOGENIC CARBON</t>
+  </si>
+  <si>
+    <t>BIOGENIC CARBON: For biogenic carbon in my LCAs, I (exclude it)</t>
+  </si>
+  <si>
+    <t>BIOGENIC CARBON: For biogenic carbon in my LCAs, I (report it separately)</t>
+  </si>
+  <si>
+    <t>BIOGENIC CARBON: The underlying assumptions are unclear</t>
+  </si>
+  <si>
+    <t>DATA</t>
+  </si>
+  <si>
+    <t>DATA: Material quantity takeoffs come from (Revit)</t>
+  </si>
+  <si>
+    <t>DATA: We request EPDs on our projects</t>
+  </si>
+  <si>
+    <t>DATA: For embodied carbon data, we use (EPDs)</t>
+  </si>
+  <si>
+    <t>DATA: Material quantity takeoffs come from (assembly factors)</t>
+  </si>
+  <si>
+    <t>DATA: For embodied carbon data, we use (EPDs from EC3)</t>
+  </si>
+  <si>
+    <t>DATA: Material quantity takeoffs come from (structural engineer)</t>
+  </si>
+  <si>
+    <t>DLCA</t>
+  </si>
+  <si>
+    <t>DLCA: I am interested to learn more about DLCA</t>
+  </si>
+  <si>
+    <t>DLCA: I have heard of DLCA, NOT</t>
+  </si>
+  <si>
+    <t>DLCA: I could incorporate DLCA in my practice</t>
+  </si>
+  <si>
+    <t>DLCA: Compared to traditional LCA, DLCA is better (accuracy)</t>
+  </si>
+  <si>
+    <t>DLCA: A barrier to adopting DLCA may be (complexity)</t>
+  </si>
+  <si>
+    <t>DLCA: DLCA seems like a good idea</t>
+  </si>
+  <si>
+    <t>LEARNING</t>
+  </si>
+  <si>
+    <t>LEARNING: A resource I use for learning LCA is (on the job)</t>
+  </si>
+  <si>
+    <t>LEARNING: A resource I use for learning LCA is (CLF)</t>
+  </si>
+  <si>
+    <t>LEARNING: A resource I use for learning LCA is (In-House Resources)</t>
+  </si>
+  <si>
+    <t>LEARNING: A resource I use for learning LCA is (SE 2050)</t>
+  </si>
+  <si>
+    <t>LEARNING: A resource I use for learning LCA is (university)</t>
+  </si>
+  <si>
+    <t>LEARNING: Before LCA work, I was already interested in (energy analysis)</t>
+  </si>
+  <si>
+    <t>MOTIVATION</t>
+  </si>
+  <si>
+    <t>MOTIVATION: Our firm's motivation for LCA is (client demand)</t>
+  </si>
+  <si>
+    <t>MOTIVATION: Our firm's motivation for LCA is (GBC - LEED)</t>
+  </si>
+  <si>
+    <t>MOTIVATION: Our firm's motivation for LCA is (EC reduction)</t>
+  </si>
+  <si>
+    <t>MOTIVATION: Our firm's motivation for LCA is (CP - SE 2050)</t>
+  </si>
+  <si>
+    <t>MOTIVATION: Our firm's motivation for LCA is (Policy)</t>
+  </si>
+  <si>
+    <t>MOTIVATION: Our firm's motivation for LCA is (institutional requirements)</t>
+  </si>
+  <si>
+    <t>MOTIVATION: Our firm's motivation for LCA is (CP - AIA 2030)</t>
+  </si>
+  <si>
+    <t>MOTIVATION: Our firm's motivation for LCA is (GBC)</t>
+  </si>
+  <si>
+    <t>OBSERVATION</t>
+  </si>
+  <si>
+    <t>OBSERVATION: LCA as a field is evolving quickly</t>
+  </si>
+  <si>
+    <t>PHASE</t>
+  </si>
+  <si>
+    <t>PHASE: Our firm generally starts LCAs during (SD)</t>
+  </si>
+  <si>
+    <t>PHASE: Our firm generally starts LCAs during (CD)</t>
+  </si>
+  <si>
+    <t>PHASE: Our firm generally starts LCAs during (DD)</t>
+  </si>
+  <si>
+    <t>PLCA</t>
+  </si>
+  <si>
+    <t>PLCA: I have heard of PLCA, NOT</t>
+  </si>
+  <si>
+    <t>PLCA: PLCA seems like a good idea</t>
+  </si>
+  <si>
+    <t>PLCA: I could incorporate PLCA in my practice</t>
+  </si>
+  <si>
+    <t>PLCA: Compared to traditional LCA, PLCA is better for (transparency)</t>
+  </si>
+  <si>
+    <t>PLCA: I am interested to learn more about PLCA</t>
+  </si>
+  <si>
+    <t>PLCA: Compared to traditional LCA, PLCA is better for (early design)</t>
+  </si>
+  <si>
+    <t>PRIORITY</t>
+  </si>
+  <si>
+    <t>PRIORITY: In LCA tools, I prioritize (ease-of-use)</t>
+  </si>
+  <si>
+    <t>PRIORITY: In LCA tools, I prioritize (cost)</t>
+  </si>
+  <si>
+    <t>PRIORITY: In LCA tools, I prioritize (interoperability with Revit)</t>
+  </si>
+  <si>
+    <t>PRIORITY: LCAs are made easier with (detailed Revit model)</t>
+  </si>
+  <si>
+    <t>PRIORITY: In LCA tools, I prioritize (quality of dataset)</t>
+  </si>
+  <si>
+    <t>PRIORITY: In LCA tools, I prioritize (EC reduction)</t>
+  </si>
+  <si>
+    <t>PRIORITY: In LCA tools, I prioritize (aligning with standards)</t>
+  </si>
+  <si>
+    <t>PRIORITY: It would be helpful if (LCA tools provided design recommendations)</t>
+  </si>
+  <si>
+    <t>PRIORITY: In LCA tools, I prioritize (inputting custom data)</t>
+  </si>
+  <si>
+    <t>PROBLEM</t>
+  </si>
+  <si>
+    <t>PROBLEM: A problem with LCAs is (data inaccuracy)</t>
+  </si>
+  <si>
+    <t>PROBLEM: A problem with LCAs is (reliability of results)</t>
+  </si>
+  <si>
+    <t>PROBLEM: It is difficult to (navigate BIM)</t>
+  </si>
+  <si>
+    <t>PROBLEM: A problem with LCAs is (lack of standardization)</t>
+  </si>
+  <si>
+    <t>PROBLEM: It is difficult to (define an EC benchmark)</t>
+  </si>
+  <si>
+    <t>PROBLEM: It is difficult to (quantify materials)</t>
+  </si>
+  <si>
+    <t>PROBLEM: A problem with LCAs is (LCAs are under valued)</t>
+  </si>
+  <si>
+    <t>PROBLEM: A problem with LCAs is (results are not interpretable)</t>
+  </si>
+  <si>
+    <t>PROBLEM: QUOTE</t>
+  </si>
+  <si>
+    <t>PROBLEM: It is difficult to (train others to do LCA)</t>
+  </si>
+  <si>
+    <t>PROBLEM: A problem with LCAs is (how much time they take, NOT)</t>
+  </si>
+  <si>
+    <t>PROBLEM: A problem with LCAs is (LCA tools are insufficient)</t>
+  </si>
+  <si>
+    <t>PROBLEM: A problem with LCAs is (cumbersome process)</t>
+  </si>
+  <si>
+    <t>PROBLEM: A problem with LCAs is (cost)</t>
+  </si>
+  <si>
+    <t>PROBLEM: It is difficult to (prioritize LCA over other work)</t>
+  </si>
+  <si>
+    <t>PROBLEM: A problem with LCAs is (how much time they take)</t>
+  </si>
+  <si>
+    <t>RESULTS</t>
+  </si>
+  <si>
+    <t>RESULTS: At the end of an LCA, results are presented in a (custom report)</t>
+  </si>
+  <si>
+    <t>RESULTS: LCA results are reported to (client)</t>
+  </si>
+  <si>
+    <t>RESULTS: Our firm keeps an internal database of (LCA results)</t>
+  </si>
+  <si>
+    <t>RESULTS: At the end of an LCA, results are presented in a (LCA tool report)</t>
+  </si>
+  <si>
+    <t>RESULTS: LCA results are reported to (CP - SE 2050)</t>
+  </si>
+  <si>
+    <t>SCOPE</t>
+  </si>
+  <si>
+    <t>SCOPE: The LCA is combined with an energy assessment</t>
+  </si>
+  <si>
+    <t>SCOPE: Our LCAs include modules (A-C)</t>
+  </si>
+  <si>
+    <t>SCOPE: Our LCAs include modules (A1-A3)</t>
+  </si>
+  <si>
     <t>SCOPE: The scope of the LCA is determined by the client</t>
   </si>
   <si>
-    <t>APPLICATION: We have worked with a sustainability consultant on the LCA</t>
-  </si>
-  <si>
-    <t>RESULTS</t>
-  </si>
-  <si>
-    <t>APPLICATION: LCA results are used to inform EC reduction</t>
-  </si>
-  <si>
-    <t>RESULTS: At the end of an LCA, results are presented in a (custom report)</t>
-  </si>
-  <si>
-    <t>RESULTS: Our firm keeps an internal database of (LCA results)</t>
-  </si>
-  <si>
-    <t>RESULTS: LCA results are reported to (client)</t>
-  </si>
-  <si>
-    <t>RESULTS: At the end of an LCA, results are presented in a (LCA tool report)</t>
-  </si>
-  <si>
-    <t>RESULTS: LCA results are reported to (CP - SE 2050)</t>
-  </si>
-  <si>
-    <t>DATA</t>
-  </si>
-  <si>
-    <t>DATA: Material quantity takeoffs come from (Revit)</t>
-  </si>
-  <si>
-    <t>DATA: We request EPDs on our projects</t>
-  </si>
-  <si>
-    <t>DATA: For embodied carbon data, we use (EPDs)</t>
-  </si>
-  <si>
-    <t>DATA: For embodied carbon data, we use (EPDs from EC3)</t>
-  </si>
-  <si>
-    <t>DATA: Material quantity takeoffs come from (assembly factors)</t>
-  </si>
-  <si>
-    <t>DATA: Material quantity takeoffs come from (structural engineer)</t>
-  </si>
-  <si>
-    <t>SCOPE</t>
-  </si>
-  <si>
-    <t>SCOPE: Our LCAs include modules (A-C)</t>
-  </si>
-  <si>
-    <t>SCOPE: Our LCAs include modules (A1-A3)</t>
-  </si>
-  <si>
-    <t>SCOPE: The LCA is combined with an energy assessment</t>
-  </si>
-  <si>
-    <t>BIOGENIC CARBON</t>
-  </si>
-  <si>
-    <t>BIOGENIC CARBON: For biogenic carbon in my LCAs, I (exclude it)</t>
-  </si>
-  <si>
-    <t>BIOGENIC CARBON: For biogenic carbon in my LCAs, I (report it separately)</t>
-  </si>
-  <si>
-    <t>BIOGENIC CARBON: The underlying assumptions are unclear</t>
-  </si>
-  <si>
-    <t>DLCA</t>
-  </si>
-  <si>
-    <t>DLCA: I am interested to learn more about DLCA</t>
-  </si>
-  <si>
-    <t>DLCA: I have heard of DLCA, NOT</t>
-  </si>
-  <si>
-    <t>DLCA: I could incorporate DLCA in my practice</t>
-  </si>
-  <si>
-    <t>DLCA: A barrier to adopting DLCA may be (complexity)</t>
-  </si>
-  <si>
-    <t>DLCA: Compared to traditional LCA, DLCA is better (accuracy)</t>
-  </si>
-  <si>
-    <t>DLCA: DLCA seems like a good idea</t>
-  </si>
-  <si>
-    <t>PLCA</t>
-  </si>
-  <si>
-    <t>PLCA: I have heard of PLCA, NOT</t>
-  </si>
-  <si>
-    <t>PLCA: PLCA seems like a good idea</t>
-  </si>
-  <si>
-    <t>PLCA: I could incorporate PLCA in my practice</t>
-  </si>
-  <si>
-    <t>PLCA: Compared to traditional LCA, PLCA is better for (transparency)</t>
-  </si>
-  <si>
-    <t>PLCA: I am interested to learn more about PLCA</t>
-  </si>
-  <si>
-    <t>PLCA: Compared to traditional LCA, PLCA is better for (early design)</t>
-  </si>
-  <si>
-    <t>RESOURCES</t>
-  </si>
-  <si>
-    <t>LEARNING: A resource I use for learning LCA is (CLF)</t>
-  </si>
-  <si>
-    <t>LEARNING: A resource I use for learning LCA is (SE 2050)</t>
-  </si>
-  <si>
-    <t>LEARNING</t>
-  </si>
-  <si>
-    <t>LEARNING: A resource I use for learning LCA is (on the job)</t>
-  </si>
-  <si>
-    <t>LEARNING: A resource I use for learning LCA is (In-House Resources)</t>
-  </si>
-  <si>
-    <t>LEARNING: A resource I use for learning LCA is (university)</t>
-  </si>
-  <si>
-    <t>MOTIVATION</t>
-  </si>
-  <si>
-    <t>MOTIVATION: Our firm's motivation for LCA is (client demand)</t>
-  </si>
-  <si>
-    <t>MOTIVATION: Our firm's motivation for LCA is (GBC - LEED)</t>
-  </si>
-  <si>
-    <t>MOTIVATION: Our firm's motivation for LCA is (EC reduction)</t>
-  </si>
-  <si>
-    <t>MOTIVATION: Our firm's motivation for LCA is (CP - SE 2050)</t>
-  </si>
-  <si>
-    <t>MOTIVATION: Our firm's motivation for LCA is (Policy)</t>
-  </si>
-  <si>
-    <t>MOTIVATION: Our firm's motivation for LCA is (institutional requirements)</t>
-  </si>
-  <si>
-    <t>MOTIVATION: Our firm's motivation for LCA is (CP - AIA 2030)</t>
-  </si>
-  <si>
-    <t>MOTIVATION: Our firm's motivation for LCA is (GBC)</t>
-  </si>
-  <si>
-    <t>OBSERVATION</t>
-  </si>
-  <si>
-    <t>OBSERVATION: LCA as a field is evolving quickly</t>
-  </si>
-  <si>
-    <t>PROBLEM</t>
-  </si>
-  <si>
-    <t>PROBLEM: A problem with LCAs is (data inaccuracy)</t>
-  </si>
-  <si>
-    <t>PROBLEM: A problem with LCAs is (reliability of results)</t>
-  </si>
-  <si>
-    <t>PROBLEM: It is difficult to (navigate BIM)</t>
-  </si>
-  <si>
-    <t>PROBLEM: A problem with LCAs is (lack of standardization)</t>
-  </si>
-  <si>
-    <t>PROBLEM: It is difficult to (define an EC benchmark)</t>
-  </si>
-  <si>
-    <t>PROBLEM: A problem with LCAs is (LCAs are under valued)</t>
-  </si>
-  <si>
-    <t>PROBLEM: It is difficult to (quantify materials)</t>
-  </si>
-  <si>
-    <t>PROBLEM: A problem with LCAs is (results are not interpretable)</t>
-  </si>
-  <si>
-    <t>PROBLEM: QUOTE</t>
-  </si>
-  <si>
-    <t>PROBLEM: A problem with LCAs is (cumbersome process)</t>
-  </si>
-  <si>
-    <t>PROBLEM: A problem with LCAs is (LCA tools are insufficient)</t>
-  </si>
-  <si>
-    <t>PROBLEM: It is difficult to (train others to do LCA)</t>
-  </si>
-  <si>
-    <t>PROBLEM: A problem with LCAs is (cost)</t>
-  </si>
-  <si>
-    <t>PROBLEM: It is difficult to (prioritize LCA over other work)</t>
-  </si>
-  <si>
-    <t>PHASE</t>
-  </si>
-  <si>
-    <t>PHASE: Our firm generally starts LCAs during (SD)</t>
-  </si>
-  <si>
-    <t>PHASE: Our firm generally starts LCAs during (CD)</t>
-  </si>
-  <si>
-    <t>PHASE: Our firm generally starts LCAs during (DD)</t>
-  </si>
-  <si>
-    <t>PRIORITY</t>
-  </si>
-  <si>
-    <t>PRIORITY: In LCA tools, I prioritize (ease-of-use)</t>
-  </si>
-  <si>
-    <t>PRIORITY: In LCA tools, I prioritize (cost)</t>
-  </si>
-  <si>
-    <t>PRIORITY: In LCA tools, I prioritize (interoperability with Revit)</t>
-  </si>
-  <si>
-    <t>PRIORITY: In LCA tools, I prioritize (quality of dataset)</t>
-  </si>
-  <si>
-    <t>PRIORITY: LCAs are made easier with (detailed Revit model)</t>
-  </si>
-  <si>
-    <t>PRIORITY: In LCA tools, I prioritize (EC reduction)</t>
-  </si>
-  <si>
-    <t>PRIORITY: In LCA tools, I prioritize (aligning with standards)</t>
-  </si>
-  <si>
-    <t>PRIORITY: In LCA tools, I prioritize (inputting custom data)</t>
-  </si>
-  <si>
     <t>TIME</t>
   </si>
   <si>
     <t>TIME: How long an LCA takes depends on (quality of Revit model)</t>
-  </si>
-  <si>
-    <t>PROBLEM: A problem with LCAs is (how much time they take, NOT)</t>
   </si>
   <si>
     <t>TOOL</t>
@@ -674,7 +680,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C115"/>
+  <dimension ref="A1:C116"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -736,10 +742,10 @@
         <v>8</v>
       </c>
       <c r="B8">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="C8">
-        <v>0.2826086956521739</v>
+        <v>0.7173913043478261</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -747,10 +753,10 @@
         <v>9</v>
       </c>
       <c r="B9">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C9">
-        <v>0.2608695652173913</v>
+        <v>0.3043478260869565</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -774,10 +780,10 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C13">
-        <v>0.5217391304347826</v>
+        <v>0.391304347826087</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -785,10 +791,10 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="C14">
-        <v>0.5</v>
+        <v>0.3478260869565217</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -796,59 +802,59 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C15">
-        <v>0.4130434782608696</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" t="s">
-        <v>15</v>
-      </c>
-      <c r="B16">
-        <v>19</v>
-      </c>
-      <c r="C16">
-        <v>0.4130434782608696</v>
+        <v>0.3043478260869565</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>16</v>
-      </c>
-      <c r="B17">
         <v>15</v>
-      </c>
-      <c r="C17">
-        <v>0.3260869565217391</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18">
+        <v>39</v>
+      </c>
+      <c r="C18">
+        <v>0.8478260869565217</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
         <v>17</v>
       </c>
-      <c r="B18">
-        <v>11</v>
-      </c>
-      <c r="C18">
-        <v>0.2391304347826087</v>
+      <c r="B19">
+        <v>27</v>
+      </c>
+      <c r="C19">
+        <v>0.5869565217391305</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
         <v>18</v>
       </c>
+      <c r="B20">
+        <v>16</v>
+      </c>
+      <c r="C20">
+        <v>0.3478260869565217</v>
+      </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
         <v>19</v>
       </c>
       <c r="B21">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="C21">
-        <v>0.8478260869565217</v>
+        <v>0.3043478260869565</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -856,10 +862,10 @@
         <v>20</v>
       </c>
       <c r="B22">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="C22">
-        <v>0.5652173913043478</v>
+        <v>0.3043478260869565</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -867,59 +873,59 @@
         <v>21</v>
       </c>
       <c r="B23">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C23">
-        <v>0.3478260869565217</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="A24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B24">
-        <v>14</v>
-      </c>
-      <c r="C24">
-        <v>0.3043478260869565</v>
+        <v>0.2173913043478261</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
-        <v>23</v>
-      </c>
-      <c r="B25">
-        <v>14</v>
-      </c>
-      <c r="C25">
-        <v>0.3043478260869565</v>
+        <v>22</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
+        <v>23</v>
+      </c>
+      <c r="B26">
+        <v>27</v>
+      </c>
+      <c r="C26">
+        <v>0.5869565217391305</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" t="s">
         <v>24</v>
       </c>
-      <c r="B26">
-        <v>10</v>
-      </c>
-      <c r="C26">
-        <v>0.2173913043478261</v>
+      <c r="B27">
+        <v>23</v>
+      </c>
+      <c r="C27">
+        <v>0.5</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
         <v>25</v>
       </c>
+      <c r="B28">
+        <v>20</v>
+      </c>
+      <c r="C28">
+        <v>0.4347826086956522</v>
+      </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" t="s">
         <v>26</v>
       </c>
       <c r="B29">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C29">
-        <v>0.391304347826087</v>
+        <v>0.2826086956521739</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -927,10 +933,10 @@
         <v>27</v>
       </c>
       <c r="B30">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C30">
-        <v>0.3478260869565217</v>
+        <v>0.2608695652173913</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -954,10 +960,10 @@
         <v>30</v>
       </c>
       <c r="B34">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="C34">
-        <v>0.391304347826087</v>
+        <v>0.5869565217391305</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -965,10 +971,10 @@
         <v>31</v>
       </c>
       <c r="B35">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C35">
-        <v>0.3478260869565217</v>
+        <v>0.3695652173913043</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -982,53 +988,53 @@
         <v>0.3043478260869565</v>
       </c>
     </row>
+    <row r="37" spans="1:3">
+      <c r="A37" t="s">
+        <v>33</v>
+      </c>
+      <c r="B37">
+        <v>13</v>
+      </c>
+      <c r="C37">
+        <v>0.2826086956521739</v>
+      </c>
+    </row>
     <row r="38" spans="1:3">
       <c r="A38" t="s">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="B38">
+        <v>11</v>
+      </c>
+      <c r="C38">
+        <v>0.2391304347826087</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B39">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="C39">
-        <v>0.5869565217391305</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3">
-      <c r="A40" t="s">
-        <v>35</v>
-      </c>
-      <c r="B40">
-        <v>23</v>
-      </c>
-      <c r="C40">
-        <v>0.5</v>
+        <v>0.2173913043478261</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
         <v>36</v>
       </c>
-      <c r="B41">
-        <v>20</v>
-      </c>
-      <c r="C41">
-        <v>0.4347826086956522</v>
-      </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" t="s">
         <v>37</v>
       </c>
       <c r="B42">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="C42">
-        <v>0.2608695652173913</v>
+        <v>0.6086956521739131</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -1036,10 +1042,10 @@
         <v>38</v>
       </c>
       <c r="B43">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="C43">
-        <v>0.2608695652173913</v>
+        <v>0.5652173913043478</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -1047,81 +1053,81 @@
         <v>39</v>
       </c>
       <c r="B44">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="C44">
-        <v>0.2173913043478261</v>
+        <v>0.5434782608695652</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" t="s">
+        <v>40</v>
+      </c>
+      <c r="B45">
+        <v>22</v>
+      </c>
+      <c r="C45">
+        <v>0.4782608695652174</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" t="s">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="B46">
+        <v>18</v>
+      </c>
+      <c r="C46">
+        <v>0.391304347826087</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B47">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="C47">
-        <v>0.6739130434782609</v>
+        <v>0.3260869565217391</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B48">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="C48">
-        <v>0.6521739130434783</v>
+        <v>0.3043478260869565</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B49">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="C49">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3">
-      <c r="A50" t="s">
-        <v>44</v>
-      </c>
-      <c r="B50">
-        <v>16</v>
-      </c>
-      <c r="C50">
-        <v>0.3478260869565217</v>
+        <v>0.2173913043478261</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51" t="s">
         <v>45</v>
       </c>
-      <c r="B51">
-        <v>13</v>
-      </c>
-      <c r="C51">
-        <v>0.2826086956521739</v>
-      </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" t="s">
         <v>46</v>
       </c>
       <c r="B52">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C52">
-        <v>0.2173913043478261</v>
+        <v>0.2826086956521739</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -1134,10 +1140,10 @@
         <v>48</v>
       </c>
       <c r="B55">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C55">
-        <v>0.3478260869565217</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -1145,37 +1151,37 @@
         <v>49</v>
       </c>
       <c r="B56">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="C56">
-        <v>0.2826086956521739</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3">
-      <c r="A58" t="s">
+        <v>0.4347826086956522</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3">
+      <c r="A57" t="s">
         <v>50</v>
+      </c>
+      <c r="B57">
+        <v>18</v>
+      </c>
+      <c r="C57">
+        <v>0.391304347826087</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59" t="s">
         <v>51</v>
       </c>
-      <c r="B59">
-        <v>27</v>
-      </c>
-      <c r="C59">
-        <v>0.5869565217391305</v>
-      </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60" t="s">
         <v>52</v>
       </c>
       <c r="B60">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="C60">
-        <v>0.2826086956521739</v>
+        <v>0.6739130434782609</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -1183,70 +1189,70 @@
         <v>53</v>
       </c>
       <c r="B61">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="C61">
-        <v>0.2391304347826087</v>
+        <v>0.6521739130434783</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3">
+      <c r="A62" t="s">
+        <v>54</v>
+      </c>
+      <c r="B62">
+        <v>23</v>
+      </c>
+      <c r="C62">
+        <v>0.5</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63" t="s">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="B63">
+        <v>16</v>
+      </c>
+      <c r="C63">
+        <v>0.3478260869565217</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B64">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="C64">
-        <v>0.6086956521739131</v>
+        <v>0.2826086956521739</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B65">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="C65">
-        <v>0.5652173913043478</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3">
-      <c r="A66" t="s">
-        <v>57</v>
-      </c>
-      <c r="B66">
-        <v>25</v>
-      </c>
-      <c r="C66">
-        <v>0.5434782608695652</v>
+        <v>0.2173913043478261</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67" t="s">
         <v>58</v>
       </c>
-      <c r="B67">
-        <v>22</v>
-      </c>
-      <c r="C67">
-        <v>0.4782608695652174</v>
-      </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68" t="s">
         <v>59</v>
       </c>
       <c r="B68">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="C68">
-        <v>0.391304347826087</v>
+        <v>0.6956521739130435</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -1254,10 +1260,10 @@
         <v>60</v>
       </c>
       <c r="B69">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C69">
-        <v>0.3260869565217391</v>
+        <v>0.4347826086956522</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -1265,10 +1271,10 @@
         <v>61</v>
       </c>
       <c r="B70">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C70">
-        <v>0.3043478260869565</v>
+        <v>0.4130434782608696</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -1276,391 +1282,419 @@
         <v>62</v>
       </c>
       <c r="B71">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C71">
-        <v>0.2173913043478261</v>
+        <v>0.3260869565217391</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3">
+      <c r="A72" t="s">
+        <v>63</v>
+      </c>
+      <c r="B72">
+        <v>15</v>
+      </c>
+      <c r="C72">
+        <v>0.3260869565217391</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73" t="s">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="B73">
+        <v>14</v>
+      </c>
+      <c r="C73">
+        <v>0.3043478260869565</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B74">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C74">
-        <v>0.2826086956521739</v>
+        <v>0.2391304347826087</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3">
+      <c r="A75" t="s">
+        <v>66</v>
+      </c>
+      <c r="B75">
+        <v>11</v>
+      </c>
+      <c r="C75">
+        <v>0.2391304347826087</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3">
-      <c r="A77" t="s">
-        <v>66</v>
-      </c>
-      <c r="B77">
-        <v>43</v>
-      </c>
-      <c r="C77">
-        <v>0.9347826086956522</v>
+        <v>67</v>
+      </c>
+      <c r="B76">
+        <v>10</v>
+      </c>
+      <c r="C76">
+        <v>0.2173913043478261</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78" t="s">
-        <v>67</v>
-      </c>
-      <c r="B78">
-        <v>27</v>
-      </c>
-      <c r="C78">
-        <v>0.5869565217391305</v>
+        <v>68</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B79">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="C79">
-        <v>0.5652173913043478</v>
+        <v>0.9347826086956522</v>
       </c>
     </row>
     <row r="80" spans="1:3">
       <c r="A80" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B80">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C80">
-        <v>0.5217391304347826</v>
+        <v>0.6086956521739131</v>
       </c>
     </row>
     <row r="81" spans="1:3">
       <c r="A81" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B81">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="C81">
-        <v>0.4130434782608696</v>
+        <v>0.5652173913043478</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B82">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C82">
-        <v>0.3478260869565217</v>
+        <v>0.5217391304347826</v>
       </c>
     </row>
     <row r="83" spans="1:3">
       <c r="A83" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B83">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C83">
-        <v>0.3043478260869565</v>
+        <v>0.4130434782608696</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B84">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C84">
-        <v>0.3043478260869565</v>
+        <v>0.391304347826087</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B85">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C85">
-        <v>0.3043478260869565</v>
+        <v>0.3478260869565217</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B86">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C86">
-        <v>0.2608695652173913</v>
+        <v>0.3043478260869565</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B87">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C87">
-        <v>0.2608695652173913</v>
+        <v>0.3043478260869565</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B88">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C88">
-        <v>0.2608695652173913</v>
+        <v>0.3043478260869565</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B89">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C89">
-        <v>0.2608695652173913</v>
+        <v>0.2826086956521739</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B90">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C90">
-        <v>0.2173913043478261</v>
+        <v>0.2608695652173913</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3">
+      <c r="A91" t="s">
+        <v>81</v>
+      </c>
+      <c r="B91">
+        <v>12</v>
+      </c>
+      <c r="C91">
+        <v>0.2608695652173913</v>
       </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92" t="s">
-        <v>80</v>
+        <v>82</v>
+      </c>
+      <c r="B92">
+        <v>12</v>
+      </c>
+      <c r="C92">
+        <v>0.2608695652173913</v>
       </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B93">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="C93">
-        <v>0.5</v>
+        <v>0.2391304347826087</v>
       </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B94">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C94">
-        <v>0.4347826086956522</v>
-      </c>
-    </row>
-    <row r="95" spans="1:3">
-      <c r="A95" t="s">
-        <v>83</v>
-      </c>
-      <c r="B95">
-        <v>18</v>
-      </c>
-      <c r="C95">
-        <v>0.391304347826087</v>
+        <v>0.2173913043478261</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3">
+      <c r="A96" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="97" spans="1:3">
       <c r="A97" t="s">
-        <v>84</v>
+        <v>86</v>
+      </c>
+      <c r="B97">
+        <v>23</v>
+      </c>
+      <c r="C97">
+        <v>0.5</v>
       </c>
     </row>
     <row r="98" spans="1:3">
       <c r="A98" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B98">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="C98">
-        <v>0.6739130434782609</v>
+        <v>0.4130434782608696</v>
       </c>
     </row>
     <row r="99" spans="1:3">
       <c r="A99" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B99">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C99">
-        <v>0.4347826086956522</v>
+        <v>0.4130434782608696</v>
       </c>
     </row>
     <row r="100" spans="1:3">
       <c r="A100" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B100">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C100">
-        <v>0.4130434782608696</v>
+        <v>0.3260869565217391</v>
       </c>
     </row>
     <row r="101" spans="1:3">
       <c r="A101" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B101">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C101">
-        <v>0.3260869565217391</v>
-      </c>
-    </row>
-    <row r="102" spans="1:3">
-      <c r="A102" t="s">
-        <v>89</v>
-      </c>
-      <c r="B102">
-        <v>15</v>
-      </c>
-      <c r="C102">
-        <v>0.3260869565217391</v>
+        <v>0.2391304347826087</v>
       </c>
     </row>
     <row r="103" spans="1:3">
       <c r="A103" t="s">
-        <v>90</v>
-      </c>
-      <c r="B103">
-        <v>14</v>
-      </c>
-      <c r="C103">
-        <v>0.3043478260869565</v>
+        <v>91</v>
       </c>
     </row>
     <row r="104" spans="1:3">
       <c r="A104" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B104">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C104">
-        <v>0.2391304347826087</v>
+        <v>0.4130434782608696</v>
       </c>
     </row>
     <row r="105" spans="1:3">
       <c r="A105" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B105">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="C105">
-        <v>0.2173913043478261</v>
+        <v>0.391304347826087</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3">
+      <c r="A106" t="s">
+        <v>94</v>
+      </c>
+      <c r="B106">
+        <v>16</v>
+      </c>
+      <c r="C106">
+        <v>0.3478260869565217</v>
       </c>
     </row>
     <row r="107" spans="1:3">
       <c r="A107" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="108" spans="1:3">
-      <c r="A108" t="s">
-        <v>94</v>
-      </c>
-      <c r="B108">
-        <v>15</v>
-      </c>
-      <c r="C108">
-        <v>0.3260869565217391</v>
+        <v>95</v>
+      </c>
+      <c r="B107">
+        <v>12</v>
+      </c>
+      <c r="C107">
+        <v>0.2608695652173913</v>
       </c>
     </row>
     <row r="109" spans="1:3">
       <c r="A109" t="s">
-        <v>95</v>
-      </c>
-      <c r="B109">
-        <v>13</v>
-      </c>
-      <c r="C109">
-        <v>0.2826086956521739</v>
-      </c>
-    </row>
-    <row r="111" spans="1:3">
-      <c r="A111" t="s">
         <v>96</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3">
+      <c r="A110" t="s">
+        <v>97</v>
+      </c>
+      <c r="B110">
+        <v>15</v>
+      </c>
+      <c r="C110">
+        <v>0.3260869565217391</v>
       </c>
     </row>
     <row r="112" spans="1:3">
       <c r="A112" t="s">
-        <v>97</v>
-      </c>
-      <c r="B112">
-        <v>28</v>
-      </c>
-      <c r="C112">
-        <v>0.6086956521739131</v>
+        <v>98</v>
       </c>
     </row>
     <row r="113" spans="1:3">
       <c r="A113" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B113">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="C113">
-        <v>0.391304347826087</v>
+        <v>0.6086956521739131</v>
       </c>
     </row>
     <row r="114" spans="1:3">
       <c r="A114" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B114">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C114">
-        <v>0.3260869565217391</v>
+        <v>0.391304347826087</v>
       </c>
     </row>
     <row r="115" spans="1:3">
       <c r="A115" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B115">
+        <v>15</v>
+      </c>
+      <c r="C115">
+        <v>0.3260869565217391</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3">
+      <c r="A116" t="s">
+        <v>102</v>
+      </c>
+      <c r="B116">
         <v>10</v>
       </c>
-      <c r="C115">
+      <c r="C116">
         <v>0.2173913043478261</v>
       </c>
     </row>
